--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486878_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486878_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. NDOUR</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8908</v>
+        <v>1.9979</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1393</v>
+        <v>1.8221</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.1759</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4278</v>
+        <v>-0.2521</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8986</v>
+        <v>-0.4601</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5291</v>
+        <v>0.208</v>
       </c>
       <c r="J2" t="n">
-        <v>1.6585</v>
+        <v>0.3182</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6191</v>
+        <v>-0.3528</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0395</v>
+        <v>0.6709000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2308</v>
+        <v>-0.5702</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.7204</v>
+        <v>-0.1074</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4897</v>
+        <v>-0.4629</v>
       </c>
       <c r="P2" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4374</v>
+        <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4445</v>
+        <v>0.1966</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5192</v>
+        <v>0.3253</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9638</v>
+        <v>-0.1287</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4189</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>O. NDOUR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8497</v>
+        <v>1.7805</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8221</v>
+        <v>1.4144</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0276</v>
+        <v>0.3662</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2521</v>
+        <v>1.4278</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4601</v>
+        <v>0.8986</v>
       </c>
       <c r="I3" t="n">
-        <v>0.208</v>
+        <v>0.5291</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3182</v>
+        <v>1.6585</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.3528</v>
+        <v>1.6191</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.0395</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5702</v>
+        <v>-0.2308</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1074</v>
+        <v>-0.7204</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4629</v>
+        <v>0.4897</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0534</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0484</v>
+        <v>0.3342</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3253</v>
+        <v>-0.2442</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2769</v>
+        <v>0.5784</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. UKAWUBA</t>
+          <t>M. VORONIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8823</v>
+        <v>1.6994</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5358000000000001</v>
+        <v>1.0179</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4181</v>
+        <v>0.6815</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5939</v>
+        <v>-0.0707</v>
       </c>
       <c r="H4" t="n">
-        <v>1.061</v>
+        <v>1.9789</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6549</v>
+        <v>-2.0495</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1026</v>
+        <v>1.5096</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2526</v>
+        <v>2.8649</v>
       </c>
       <c r="L4" t="n">
         <v>-1.3552</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4913</v>
+        <v>-1.5803</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1917</v>
+        <v>-0.886</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2996</v>
+        <v>-0.6943</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8481</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5238</v>
+        <v>-0.0513</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5851</v>
+        <v>-0.0544</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0613</v>
+        <v>0.003</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>0.5893</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VORONIN</t>
+          <t>R. UKAWUBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7778</v>
+        <v>1.4604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3631</v>
+        <v>-0.1948</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4147</v>
+        <v>1.6552</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0707</v>
+        <v>-0.5939</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9789</v>
+        <v>1.061</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.0495</v>
+        <v>-1.6549</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5096</v>
+        <v>-0.1026</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8649</v>
+        <v>1.2526</v>
       </c>
       <c r="L5" t="n">
         <v>-1.3552</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5803</v>
+        <v>-0.4913</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.886</v>
+        <v>-0.1917</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6943</v>
+        <v>-0.2996</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9729</v>
+        <v>0.0543</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7091</v>
+        <v>-0.2442</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2637</v>
+        <v>0.2985</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5893</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.7713</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4084</v>
+        <v>-0.0675</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9573</v>
+        <v>0.8388</v>
       </c>
       <c r="G6" t="n">
         <v>1.8139</v>
@@ -922,13 +922,13 @@
         <v>3.0801</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1108</v>
+        <v>0.3332</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3257</v>
+        <v>0.0153</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4365</v>
+        <v>0.318</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3491</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. SOUMBEY-ALLEY</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0878</v>
+        <v>0.0258</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2089</v>
+        <v>0.0549</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2967</v>
+        <v>-0.0291</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6463</v>
+        <v>-1.4503</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0484</v>
+        <v>-0.461</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6947</v>
+        <v>-0.9893</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2457</v>
+        <v>0.0434</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0881</v>
+        <v>0.1752</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1575</v>
+        <v>-0.1318</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-1.4937</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1365</v>
+        <v>-0.6362</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4629</v>
+        <v>-0.8575</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.8481</v>
+        <v>1.6427</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1756</v>
+        <v>-0.1666</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3139</v>
+        <v>0.0115</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4895</v>
+        <v>-0.1781</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9384</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3573</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. FOLLA-CISNEROS GIMENO</t>
+          <t>L. SOUMBEY-ALLEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1853</v>
+        <v>-0.0861</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0395</v>
+        <v>0.4181</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.2247</v>
+        <v>-0.5042</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4104</v>
+        <v>0.6463</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1947</v>
+        <v>-0.0484</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2157</v>
+        <v>0.6947</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0395</v>
+        <v>1.2457</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.0881</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0395</v>
+        <v>1.1575</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4498</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1947</v>
+        <v>-0.1365</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2552</v>
+        <v>-0.4629</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0198</v>
+        <v>0.1773</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.1047</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0198</v>
+        <v>0.282</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.9384</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>G. FOLLA-CISNEROS GIMENO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6157</v>
+        <v>-0.1556</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4681</v>
+        <v>0.0395</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1476</v>
+        <v>-0.1951</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4503</v>
+        <v>-0.4104</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.461</v>
+        <v>-0.1947</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9893</v>
+        <v>-0.2157</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0434</v>
+        <v>0.0395</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1752</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1318</v>
+        <v>0.0395</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4937</v>
+        <v>-0.4498</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6362</v>
+        <v>-0.1947</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8575</v>
+        <v>-0.2552</v>
       </c>
       <c r="P10" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8082</v>
+        <v>0.0494</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5115</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2967</v>
+        <v>0.0494</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7542</v>
+        <v>-1.3456</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1326</v>
+        <v>-0.4292</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8868</v>
+        <v>-0.9164</v>
       </c>
       <c r="G11" t="n">
         <v>-2.2799</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0883</v>
+        <v>0.4969</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5538</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5345</v>
+        <v>0.5048</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5893</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4256</v>
+        <v>-4.6083</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3197</v>
+        <v>-2.4432</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1058</v>
+        <v>-2.1651</v>
       </c>
       <c r="G12" t="n">
         <v>-3.1868</v>
@@ -1390,13 +1390,13 @@
         <v>1.4374</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7736</v>
+        <v>0.5908</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8517</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.1374</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3963</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0862</v>
+        <v>1.745</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9735</v>
+        <v>1.632200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1128999999999998</v>
+        <v>0.1130000000000004</v>
       </c>
       <c r="G13" t="n">
         <v>-4.3561</v>
       </c>
       <c r="H13" t="n">
-        <v>3.878099999999999</v>
+        <v>3.8781</v>
       </c>
       <c r="I13" t="n">
         <v>-8.2342</v>
@@ -1459,7 +1459,7 @@
         <v>-5.785799999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>5.1335</v>
+        <v>5.133500000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.3204</v>
@@ -1468,10 +1468,10 @@
         <v>17.454</v>
       </c>
       <c r="S13" t="n">
-        <v>1.3561</v>
+        <v>2.0148</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2337</v>
+        <v>0.4249999999999999</v>
       </c>
       <c r="U13" t="n">
         <v>1.5899</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3479</v>
+        <v>5.9319</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8144</v>
+        <v>4.1282</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5335</v>
+        <v>1.8037</v>
       </c>
       <c r="G14" t="n">
         <v>4.2215</v>
@@ -1546,13 +1546,13 @@
         <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3932</v>
+        <v>0.1908</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.651</v>
+        <v>-0.3372</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2578</v>
+        <v>0.528</v>
       </c>
       <c r="V14" t="n">
         <v>0.6982</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>K. JOHNSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9496</v>
+        <v>3.7369</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4288</v>
+        <v>2.1692</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5208</v>
+        <v>1.5677</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2971</v>
+        <v>2.1096</v>
       </c>
       <c r="H15" t="n">
-        <v>2.384</v>
+        <v>0.8467</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.08699999999999999</v>
+        <v>1.2629</v>
       </c>
       <c r="J15" t="n">
-        <v>2.2696</v>
+        <v>2.3029</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8225</v>
+        <v>1.6454</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5528999999999999</v>
+        <v>0.6575</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0274</v>
+        <v>-0.1933</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4385</v>
+        <v>-0.7987</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4659</v>
+        <v>0.6054</v>
       </c>
       <c r="P15" t="n">
+        <v>-1.8481</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-3.2855</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.4374</v>
       </c>
-      <c r="Q15" t="n">
-        <v>-0.2053</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.6427</v>
-      </c>
       <c r="S15" t="n">
-        <v>-0.1956</v>
+        <v>0.2886</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2249</v>
+        <v>-0.0351</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0293</v>
+        <v>0.3237</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5893</v>
+        <v>3.1868</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5893</v>
+        <v>3.1868</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. PAZ VAZQUEZ</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6394</v>
+        <v>3.0803</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6481</v>
+        <v>2.4288</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.6515</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2664</v>
+        <v>2.2971</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0062</v>
+        <v>2.384</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2602</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.2682</v>
+        <v>2.2696</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0317</v>
+        <v>2.8225</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2365</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0017</v>
+        <v>0.0274</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0255</v>
+        <v>-0.4385</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0238</v>
+        <v>0.4659</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.616</v>
+        <v>1.4374</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>2.2292</v>
+        <v>-0.0649</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4333</v>
+        <v>-0.2249</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2402</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. JOHNSON</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3316</v>
+        <v>2.1134</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8554</v>
+        <v>1.1945</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4763</v>
+        <v>0.9189000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1096</v>
+        <v>2.2754</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8467</v>
+        <v>1.1838</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2629</v>
+        <v>1.0916</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3029</v>
+        <v>2.3584</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6454</v>
+        <v>1.8721</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6575</v>
+        <v>0.4863</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1933</v>
+        <v>-0.083</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7987</v>
+        <v>-0.6883</v>
       </c>
       <c r="O17" t="n">
         <v>0.6054</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8481</v>
+        <v>-3.6962</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.2855</v>
+        <v>-5.1336</v>
       </c>
       <c r="R17" t="n">
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1167</v>
+        <v>0.6964</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3489</v>
+        <v>-0.0467</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7678</v>
+        <v>0.7431</v>
       </c>
       <c r="V17" t="n">
-        <v>3.1868</v>
+        <v>2.8377</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1868</v>
+        <v>4.0164</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>S. PAZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5399</v>
+        <v>1.555</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0899</v>
+        <v>0.602</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4499</v>
+        <v>0.953</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2754</v>
+        <v>1.2664</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1838</v>
+        <v>0.0062</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0916</v>
+        <v>1.2602</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3584</v>
+        <v>2.2682</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8721</v>
+        <v>1.0317</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4863</v>
+        <v>1.2365</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.083</v>
+        <v>-1.0017</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6883</v>
+        <v>-1.0255</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6054</v>
+        <v>0.0238</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.6962</v>
+        <v>-0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.1336</v>
+        <v>-2.0534</v>
       </c>
       <c r="R18" t="n">
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1229</v>
+        <v>1.1448</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1513</v>
+        <v>0.3873</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2741</v>
+        <v>0.7575</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8377</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>4.0164</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4743</v>
+        <v>0.1516</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0007</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5264</v>
+        <v>1.1523</v>
       </c>
       <c r="G19" t="n">
         <v>-1.9151</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1615</v>
+        <v>0.7874</v>
       </c>
       <c r="T19" t="n">
         <v>-0.0195</v>
       </c>
       <c r="U19" t="n">
-        <v>0.181</v>
+        <v>0.8069</v>
       </c>
       <c r="V19" t="n">
         <v>0.4579</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7491</v>
+        <v>-0.4806</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1103</v>
+        <v>0.0989</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6388</v>
+        <v>-0.5795</v>
       </c>
       <c r="G20" t="n">
         <v>0.5752</v>
@@ -2014,13 +2014,13 @@
         <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7082000000000001</v>
+        <v>-0.4398</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3294</v>
+        <v>-0.1202</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3789</v>
+        <v>-0.3196</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9784</v>
+        <v>-1.1475</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3954</v>
+        <v>-0.8138</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5829</v>
+        <v>-0.3336</v>
       </c>
       <c r="G21" t="n">
         <v>-1.3533</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9643</v>
+        <v>0.7951</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6778</v>
+        <v>0.2594</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2864</v>
+        <v>0.5357</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5893</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1089</v>
+        <v>-3.102</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.6221</v>
+        <v>-2.5175</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4869</v>
+        <v>-0.5845</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1253</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.805</v>
+        <v>-0.7981</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6587</v>
+        <v>-0.5541</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1463</v>
+        <v>-0.244</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9249</v>
+        <v>-3.6721</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6012</v>
+        <v>-2.4966</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3237</v>
+        <v>-1.1755</v>
       </c>
       <c r="G23" t="n">
         <v>-2.721</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6412</v>
+        <v>-0.3884</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4611</v>
+        <v>-0.3565</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1801</v>
+        <v>-0.0319</v>
       </c>
       <c r="V23" t="n">
         <v>-1.1786</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.6591</v>
+        <v>-6.4639</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2199</v>
+        <v>-3.906</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4393</v>
+        <v>-2.5578</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2744</v>
@@ -2326,13 +2326,13 @@
         <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.974</v>
+        <v>-0.7788</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8563</v>
+        <v>-0.5425</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1177</v>
+        <v>-0.2362</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3573</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0863</v>
+        <v>1.702999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1129999999999987</v>
+        <v>-0.113</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9732999999999996</v>
+        <v>1.816200000000001</v>
       </c>
       <c r="G25" t="n">
         <v>4.3561</v>
@@ -2380,7 +2380,7 @@
         <v>10.8983</v>
       </c>
       <c r="K25" t="n">
-        <v>5.112200000000001</v>
+        <v>5.112199999999999</v>
       </c>
       <c r="L25" t="n">
         <v>5.785899999999999</v>
@@ -2404,13 +2404,13 @@
         <v>12.3207</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.356</v>
+        <v>1.4331</v>
       </c>
       <c r="T25" t="n">
         <v>-1.59</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2336999999999999</v>
+        <v>3.0232</v>
       </c>
       <c r="V25" t="n">
         <v>1.047299999999999</v>
